--- a/resources/library/xlsx/restaurant-audit-scorecard.xlsx
+++ b/resources/library/xlsx/restaurant-audit-scorecard.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessment" sheetId="1" r:id="Reda91a448dd44887"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="Rc0b9f3c195df465e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R9c5c808e71744f0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessment" sheetId="1" r:id="R3d27096aa32a45e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="Rb4920c717d73416a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="Re309b79bafad4b12"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -184,6 +184,102 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="28706e5c-2caf-4cf5-b18f-b170c6f2b8a7"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rd6bb88f1a23e48b8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="422bd8c0-064b-4a36-883c-9b47fa8e7005"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rbb12c05393bd4987"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="64f4fcc4-2a4d-47a7-8e0b-f723fa52bdf6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R66afb642c96440c4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -388,7 +484,7 @@
     <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="19"/>
       <x:c r="B1" s="19"/>
       <x:c r="C1" s="19"/>
@@ -1533,6 +1629,7 @@
     <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra277f52d059e4e10"/>
 </x:worksheet>
 </file>
 
@@ -1547,7 +1644,7 @@
     <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="19"/>
       <x:c r="B1" s="19"/>
       <x:c r="C1" s="19"/>
@@ -2608,6 +2705,7 @@
     <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a4803c59a014ad2"/>
 </x:worksheet>
 </file>
 
@@ -2622,7 +2720,7 @@
     <x:col min="2" max="2" width="80" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="19"/>
       <x:c r="B1" s="19"/>
       <x:c r="C1" s="19"/>
@@ -3688,5 +3786,6 @@
     <x:mergeCell ref="A5:H5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56e787406d7b4b17"/>
 </x:worksheet>
 </file>